--- a/mode_docx_gen/pmi_gz/gzrpn_modes/ГЗ РПН_12.xlsx
+++ b/mode_docx_gen/pmi_gz/gzrpn_modes/ГЗ РПН_12.xlsx
@@ -782,35 +782,35 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1242,8 +1242,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1353,8 +1353,8 @@
       <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="AL2" s="2" t="n">
-        <v>1</v>
+      <c r="AL2" t="n">
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -2104,9 +2104,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AX2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2124,9 +2124,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -2139,9 +2139,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -2149,9 +2149,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -2234,9 +2234,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BX2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
